--- a/reports/集团总公司_利润表_2025-12.xlsx
+++ b/reports/集团总公司_利润表_2025-12.xlsx
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>213425649</v>
+        <v>231373319</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>162492036</v>
+        <v>175573839</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>2018983738</v>
+        <v>2189205501</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>658232</v>
+        <v>856050</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>8225899</v>
+        <v>10653892</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>569952</v>
+        <v>747859</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>7135559</v>
+        <v>9323439</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>485561</v>
+        <v>630223</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>6046498</v>
+        <v>7870577</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>445369</v>
+        <v>580770</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>5562612</v>
+        <v>7264382</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>243522</v>
+        <v>318987</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>3023467</v>
+        <v>3994507</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>194193</v>
+        <v>251149</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>2419250</v>
+        <v>3146354</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>210828820</v>
+        <v>227988281</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>159895207</v>
+        <v>172188801</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>82327968</v>
+        <v>89313800</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>1023088681</v>
+        <v>1118759459</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1507437</v>
+        <v>2669387</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>18768499</v>
+        <v>33255428</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>1355959</v>
+        <v>1943795</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>16949527</v>
+        <v>24185641</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2405,10 +2405,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>73107247</v>
+        <v>77013579</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>907555419</v>
+        <v>955475549</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1543473</v>
+        <v>1949448</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>19363122</v>
+        <v>24198722</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>679663</v>
+        <v>974003</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>8471119</v>
+        <v>12103107</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2411846</v>
+        <v>2920914</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>30249770</v>
+        <v>36321883</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>1065880</v>
+        <v>1458300</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>13306100</v>
+        <v>18161140</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>50763899</v>
+        <v>50505670</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>632831537</v>
+        <v>633159174</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>169714</v>
+        <v>169582</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>2039270</v>
+        <v>2041162</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>3075789</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>38497241</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>2048439</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>25658416</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>154364338</v>
+        <v>173773987</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>123917527</v>
+        <v>129929692</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>97713613</v>
+        <v>103542456</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>1212032456</v>
+        <v>1296526999</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2737,10 +2737,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>26203914</v>
+        <v>26387236</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>327930701</v>
+        <v>327696168</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>5144036</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>64085302</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2793,10 +2793,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>1648816</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>20509631</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>1031806</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>12821296</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>1238961</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>15389879</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>929140</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>11545827</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -2905,10 +2905,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>618932</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>7699213</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -2933,10 +2933,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>515070</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>6417144</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>2869532</v>
+        <v>2859213</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>35685456</v>
+        <v>35718778</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>1343802</v>
+        <v>1348250</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>16810609</v>
+        <v>16833511</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>3500491</v>
+        <v>3476292</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>43551610</v>
+        <v>43559328</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3045,10 +3045,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>22601637</v>
+        <v>22507985</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>281897714</v>
+        <v>281857167</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>351297</v>
+        <v>2757444</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>4198797</v>
+        <v>34457436</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>1123854</v>
+        <v>1116600</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>13440350</v>
+        <v>13432749</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>1159385</v>
+        <v>1067562</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>13921901</v>
+        <v>12834122</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>120550</v>
+        <v>119844</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>1440529</v>
+        <v>1438884</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>477393</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>5719588</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>901873</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>11216469</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3241,10 +3241,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>319155</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>3814616</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3269,10 +3269,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>239497</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>2861881</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>399088</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>4771377</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>1289244</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>16040491</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>212355</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>2545902</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3381,10 +3381,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>158991</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>1909512</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>264529</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>3182229</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>184909</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>2227082</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3465,10 +3465,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>131965</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>1590292</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>105559</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>1271812</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>79216</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>953566</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3549,7 +3549,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>56464482</v>
+        <v>57412652</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>61007506</v>
+        <v>61465144</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>514642</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>6408652</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>132849</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>1589058</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>210297</v>
+        <v>210782</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>2520952</v>
+        <v>2519184</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>56254185</v>
+        <v>57716512</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>7108145</v>
+        <v>7128801</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>85205404</v>
+        <v>85225184</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3739,7 +3739,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>49146040</v>
+        <v>50587711</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>49146040</v>
+        <v>50587711</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>49146040</v>
+        <v>50587711</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>49146040</v>
+        <v>50587711</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4067,7 +4067,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>49146040</v>
+        <v>50587711</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
